--- a/tasks/9-28_Jobs_Review_Companion.xlsx
+++ b/tasks/9-28_Jobs_Review_Companion.xlsx
@@ -10,9 +10,10 @@
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Deprioritized" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Call Accuracy Review" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Est. Jobs" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Priority Oppty Set" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Appendix Contact Outreach" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Devika Coverage" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Est. Jobs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Priority Oppty Set" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Appendix Contact Outreach" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51,7 +52,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +74,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -104,6 +110,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -598,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4761,9 +4770,2577 @@
       </c>
       <c r="E179" s="2" t="inlineStr"/>
     </row>
+    <row r="180">
+      <c r="A180" s="5" t="inlineStr">
+        <is>
+          <t>645 Ventures</t>
+        </is>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined (VC). No update since 7/30. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E180" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>a16z (Andreessen Horowitz)</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined (VC). No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined (PE). No update since 7/24. Avni also has a KKR contact in initial outreach. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="inlineStr">
+        <is>
+          <t>TPG</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C183" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined (PE). No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="inlineStr">
+        <is>
+          <t>Silver Lake</t>
+        </is>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C184" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined (PE). No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E184" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="5" t="inlineStr">
+        <is>
+          <t>Union Square Ventures (USV)</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C185" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined (VC). No update since 8/12. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="inlineStr">
+        <is>
+          <t>Primary Ventures</t>
+        </is>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C186" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined (VC). No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="inlineStr">
+        <is>
+          <t>Maverick Capital Partners</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C187" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined. No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="inlineStr">
+        <is>
+          <t>AHP / Assured Healthcare Partners</t>
+        </is>
+      </c>
+      <c r="B188" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C188" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="inlineStr">
+        <is>
+          <t>Two open opps (FT, Medium; part-time/contract, Medium), Active in Discussions (healthcare PE). No update since 8/12. Likely duplicate records; merge in Bedrock. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E188" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="inlineStr">
+        <is>
+          <t>Tenex</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C189" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>Open opp: AI Hiring, 1 role, Active in Discussions, likelihood Medium. No update since 7/30. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E189" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRM WITH DEVIKA: defined role, Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Benchstrength</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined. No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Macquarie</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined. No update since 6/18. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Marsh McLennan</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined. No update since 7/21. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined. No update since 6/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>OpenRouter</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, likelihood Low. No update since 8/12. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Alphadyne Asset Management</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Angi</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Anna-Maria and Stephen Kellen Foundation</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Arcadia</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Audible</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="5" t="inlineStr">
+        <is>
+          <t>Bain Capital Ventures</t>
+        </is>
+      </c>
+      <c r="B205" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C205" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="inlineStr">
+        <is>
+          <t>Betaworks</t>
+        </is>
+      </c>
+      <c r="B207" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C207" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Bluecore</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>BNY Mellon</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Brooklyn Navy Yard Development Corporation</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>CBRE</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Cedar</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="inlineStr">
+        <is>
+          <t>Clayton, Dubilier &amp; Rice (CDR)</t>
+        </is>
+      </c>
+      <c r="B215" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Consensys</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Costco</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="5" t="inlineStr">
+        <is>
+          <t>DataPower Capital</t>
+        </is>
+      </c>
+      <c r="B218" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C218" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D218" s="5" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Deutsche Bank</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Elastic</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Etsy</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Flatiron Health</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Foursquare</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>F&amp;T Group</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="inlineStr">
+        <is>
+          <t>General Atlantic</t>
+        </is>
+      </c>
+      <c r="B226" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C226" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D226" s="5" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Get Real Labs</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>iCapital</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Inherent Group</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>JFF (Jobs for the Future)</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Justworks</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Latinos United for Change (LUCHA)</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Link Logistics</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>L&amp;L Foundation</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>London Stock Exchange Group</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="5" t="inlineStr">
+        <is>
+          <t>Maverick Capital Foundation</t>
+        </is>
+      </c>
+      <c r="B242" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C242" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D242" s="5" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E242" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="inlineStr">
+        <is>
+          <t>Maycomb Capital</t>
+        </is>
+      </c>
+      <c r="B243" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C243" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="5" t="inlineStr">
+        <is>
+          <t>MLT (Management Leadership for Tomorrow)</t>
+        </is>
+      </c>
+      <c r="B246" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C246" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D246" s="5" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized. Updated 9/23, so there may be recent activity.</t>
+        </is>
+      </c>
+      <c r="E246" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRM WITH DEVIKA: recent activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>National Grid Foundation</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>New York State - ITS Sector</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>New York Times</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>NJ AI Hub</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Nova Credit</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Optimum</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Orr Group</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>PDT Partners</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Peloton</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Plaxall</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>PNC Financial</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Poll Everywhere</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Priceline</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="5" t="inlineStr">
+        <is>
+          <t>Primary VC</t>
+        </is>
+      </c>
+      <c r="B264" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D264" s="5" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Red Canary</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Sales Edge Solutions</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>SeatGeek</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Siegel Family Endowment</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Spring Health</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Stealth Startup</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Stephen A. Schwarzman Foundation</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>TD Bank</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="inlineStr">
+        <is>
+          <t>Techstars</t>
+        </is>
+      </c>
+      <c r="B273" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C273" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D273" s="5" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>TF Cornerstone</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>The Apollo Opportunity Foundation</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C275" s="5" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D275" s="5" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized. Related to Apollo, which Devika said to keep working; confirm whether it rides with Apollo.</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRM WITH DEVIKA: tied to Apollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>The Knot Worldwide</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Thumbtack</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>United Federation of Teachers (UFT)</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Urban Upbound</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Venmo / PayPal</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Verizon</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Western Union Foundation</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Workforce Development Corporation</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>Devika Gopal Agge</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B2:B179" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B287" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5311,6 +7888,3544 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E132"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="100" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Devika: 19 pursuing, 21 confirm, 88 not pursuing, 1 closed won (129 total)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>In Bedrock as</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Open opps (Bedrock)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Where it sits / why</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Not in Bedrock</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed; intro offered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Account + opp</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>1 (Builder Submitted, Low)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed; 1 open-market role.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Apollo Global Management</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Account + opp</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>1 (Active in Discussions, Medium)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Discussed ('slower, keep working') but MISSING from Priority Oppty Set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Blackstone</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Opps only (no account record)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>7 records (4 role-level)</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed; 2-3 likely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed; no bite yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>Account + opp</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>1 (5 roles, Confirmed, Medium)</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed on call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Con Edison</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set (ConEd, listed under Avni).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Girls Who Code</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Not in Bedrock</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed; activate via incoming CEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed; grant multiplayer, Q1 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Gutter Capital / Switchboard / Faraday</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Accounts + opps</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Switchboard 1, Faraday 2, Gutter 1</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set (Gutter/ Switchboard). Faraday may be undercounted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Hispanic Federation</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Account + opp</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>1 (2 roles, Medium)</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set (listed under Avni).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Not in Bedrock</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Discussed ('slower, keep working') but MISSING from Priority Oppty Set and Bedrock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>JP Morgan / JPMC</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Account + opp</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>3 (New cohort 3 roles, Current cohort conversion 2, Sr. Assoc AI PMO 1)</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed on call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Morgan Stanley</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Murmuration</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Account; opps owned by Avni</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>2 (Builder Submitted)</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed; open market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Newmark (NMRK)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Account + opp</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>1 (Research Analyst, Low)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed; open market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Pharma Logistics</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Account; opp owned by Avni</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>1 (Builder Submitted)</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Renaissance Philanthropy</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set (RenPhil). Talent accelerator pilot call scheduled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>RXR</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Pursuing</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Priority set only</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Opp owned by Avni</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>Priority Oppty Set. Discussed; Avni managing day to day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>645 Ventures</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. Open opp, Active in Discussions, no roles defined (VC). No update since 7/30. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>a16z (Andreessen Horowitz)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. Open opp, Active in Discussions, no roles defined (VC). No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>AHP / Assured Healthcare Partners</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. Two open opps (FT, Medium; part-time/contract, Medium), Active in Discussions (healthcare PE). No update since 8/12. Likely duplicate records; merge in Bedrock. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Bain Capital Ventures</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Betaworks</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Clayton, Dubilier &amp; Rice (CDR)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>DataPower Capital</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>General Atlantic</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>KKR</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. Open opp, Active in Discussions, no roles defined (PE). No update since 7/24. Avni also has a KKR contact in initial outreach. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Maverick Capital Foundation</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Maverick Capital Partners</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. Open opp, Active in Discussions, no roles defined. No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Maycomb Capital</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>MLT (Management Leadership for Tomorrow)</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRM WITH DEVIKA: recent activity. There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized. Updated 9/23, so there may be recent activity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Primary VC</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Primary Ventures</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. Open opp, Active in Discussions, no roles defined (VC). No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Silver Lake</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. Open opp, Active in Discussions, no roles defined (PE). No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Techstars</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Tenex</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRM WITH DEVIKA: defined role, Medium. Open opp: AI Hiring, 1 role, Active in Discussions, likelihood Medium. No update since 7/30. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>The Apollo Opportunity Foundation</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>CONFIRM WITH DEVIKA: tied to Apollo. There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized. Related to Apollo, which Devika said to keep working; confirm whether it rides with Apollo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>TPG</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. Open opp, Active in Discussions, no roles defined (PE). No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Union Square Ventures (USV)</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Confirm</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>SOURCING CHANNEL: confirm with Devika before deprioritizing. Open opp, Active in Discussions, no roles defined (VC). No update since 8/12. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Alphadyne Asset Management</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Angi</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Anna-Maria and Stephen Kellen Foundation</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Arcadia</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Audible</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Autodesk</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Benchstrength</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined. No update since 7/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Bluecore</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>BNY Mellon</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Brooklyn Navy Yard Development Corporation</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>CBRE</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Cedar</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Account</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Discussed on call: deprioritized (own bootcamp, no DEI hiring partners).</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Consensys</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Costco</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Deutsche Bank</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Elastic</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Etsy</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>F&amp;T Group</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Flatiron Health</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Foursquare</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Get Real Labs</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Greenhouse</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>iCapital</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Inherent Group</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>JFF (Jobs for the Future)</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Justworks</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>L&amp;L Foundation</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Latinos United for Change (LUCHA)</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Link Logistics</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>London Stock Exchange Group</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Macquarie</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined. No update since 6/18. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Marsh McLennan</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined. No update since 7/21. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, no roles defined. No update since 6/24. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Moody's</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>National Grid Foundation</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>New York State - ITS Sector</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>New York Times</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>NJ AI Hub</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Nova Credit</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>OpenRouter</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Opp</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>1+</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Open opp, Active in Discussions, likelihood Low. No update since 8/12. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Optimum</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Orr Group</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Oscar</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>PDT Partners</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Peloton</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Plaxall</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>PNC Financial</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Poll Everywhere</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Priceline</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Red Canary</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Sales Edge Solutions</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>SeatGeek</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Siegel Family Endowment</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Spring Health</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Stealth Startup</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Stephen A. Schwarzman Foundation</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>TD Bank</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>TF Cornerstone</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>The Knot Worldwide</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Thumbtack</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>United Federation of Teachers (UFT)</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Urban Upbound</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Venmo / PayPal</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Verizon</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Western Union Foundation</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Workforce Development Corporation</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Not pursuing</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Account (no opp)</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>There was an account for outreach. Part of Devika's Bedrock account pool (bulk-assigned 7/29); no opportunity and no logged movement since. Not discussed on 9/28 call; assume deprioritized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Cypress Hills Development Corporation</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Closed won</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Account + opp</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Closed Won</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Past placement; not an active pursuit. Keep as relationship.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5460,7 +11575,7 @@
           <t>Probability-weighted: Q4 2026</t>
         </is>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="8">
         <f>SUMIFS('Priority Oppty Set'!$E$2:$E$200,'Priority Oppty Set'!$F$2:$F$200,"&gt;="&amp;$B$18,'Priority Oppty Set'!$F$2:$F$200,"&lt;="&amp;$B$19,'Priority Oppty Set'!$H$2:$H$200,"High")*$B$24+SUMIFS('Priority Oppty Set'!$E$2:$E$200,'Priority Oppty Set'!$F$2:$F$200,"&gt;="&amp;$B$18,'Priority Oppty Set'!$F$2:$F$200,"&lt;="&amp;$B$19,'Priority Oppty Set'!$H$2:$H$200,"Medium")*$B$25+SUMIFS('Priority Oppty Set'!$E$2:$E$200,'Priority Oppty Set'!$F$2:$F$200,"&gt;="&amp;$B$18,'Priority Oppty Set'!$F$2:$F$200,"&lt;="&amp;$B$19,'Priority Oppty Set'!$H$2:$H$200,"Low")*$B$26</f>
         <v/>
       </c>
@@ -5481,7 +11596,7 @@
           <t>Probability-weighted: Q3 2027</t>
         </is>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <f>SUMIFS('Priority Oppty Set'!$E$2:$E$200,'Priority Oppty Set'!$F$2:$F$200,"&gt;="&amp;$B$20,'Priority Oppty Set'!$F$2:$F$200,"&lt;="&amp;$B$21,'Priority Oppty Set'!$H$2:$H$200,"High")*$B$24+SUMIFS('Priority Oppty Set'!$E$2:$E$200,'Priority Oppty Set'!$F$2:$F$200,"&gt;="&amp;$B$20,'Priority Oppty Set'!$F$2:$F$200,"&lt;="&amp;$B$21,'Priority Oppty Set'!$H$2:$H$200,"Medium")*$B$25+SUMIFS('Priority Oppty Set'!$E$2:$E$200,'Priority Oppty Set'!$F$2:$F$200,"&gt;="&amp;$B$20,'Priority Oppty Set'!$F$2:$F$200,"&lt;="&amp;$B$21,'Priority Oppty Set'!$H$2:$H$200,"Low")*$B$26</f>
         <v/>
       </c>
@@ -5530,7 +11645,7 @@
           <t>Goal by EOQ4 2026</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="9" t="n">
         <v>35</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -5573,7 +11688,7 @@
           <t>Q4 2026 start</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="10" t="n">
         <v>46296</v>
       </c>
     </row>
@@ -5583,7 +11698,7 @@
           <t>Q4 2026 end</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B19" s="10" t="n">
         <v>46387</v>
       </c>
     </row>
@@ -5593,7 +11708,7 @@
           <t>Q3 2027 window start</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="10" t="n">
         <v>46388</v>
       </c>
     </row>
@@ -5603,7 +11718,7 @@
           <t>Q3 2027 window end</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n">
+      <c r="B21" s="10" t="n">
         <v>46660</v>
       </c>
     </row>
@@ -5620,7 +11735,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="11" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -5630,7 +11745,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n">
+      <c r="B25" s="11" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5640,7 +11755,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B26" s="11" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -5649,7 +11764,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5740,7 +11855,7 @@
       <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="11" t="n">
+      <c r="F2" s="12" t="n">
         <v>46325</v>
       </c>
       <c r="G2" t="inlineStr">
@@ -5783,7 +11898,7 @@
       <c r="E3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="12" t="n">
         <v>46325</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -5891,7 +12006,7 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="12" t="n">
         <v>46325</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -5934,7 +12049,7 @@
       <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="12" t="n">
         <v>46325</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -6141,7 +12256,7 @@
           <t>Devika Gopal Agge</t>
         </is>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="12" t="n">
         <v>46477</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -6174,7 +12289,7 @@
       <c r="E16" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="11" t="n">
+      <c r="F16" s="12" t="n">
         <v>46325</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -6234,7 +12349,7 @@
       <c r="E18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="12" t="n">
         <v>46477</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -6272,7 +12387,7 @@
       <c r="E19" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="12" t="n">
         <v>46325</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -6305,7 +12420,7 @@
       <c r="E20" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="12" t="n">
         <v>46381</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -6338,7 +12453,7 @@
       <c r="E21" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="12" t="n">
         <v>46325</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -6371,7 +12486,7 @@
       <c r="E22" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="11" t="n">
+      <c r="F22" s="12" t="n">
         <v>46381</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -6404,7 +12519,7 @@
       <c r="E23" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="12" t="n">
         <v>46381</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -6437,7 +12552,7 @@
       <c r="E24" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="12" t="n">
         <v>46381</v>
       </c>
       <c r="G24" t="inlineStr">
@@ -6470,7 +12585,7 @@
       <c r="E25" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="12" t="n">
         <v>46381</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -6503,7 +12618,7 @@
       <c r="E26" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="12" t="n">
         <v>46381</v>
       </c>
       <c r="G26" t="inlineStr">
@@ -6536,7 +12651,7 @@
       <c r="E27" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="12" t="n">
         <v>46325</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -6569,7 +12684,7 @@
       <c r="E28" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="11" t="n">
+      <c r="F28" s="12" t="n">
         <v>46381</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -6607,7 +12722,7 @@
       <c r="E29" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F29" s="12" t="n">
         <v>46381</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -6645,7 +12760,7 @@
       <c r="E30" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="12" t="n">
         <v>46381</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -6664,7 +12779,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
